--- a/Projects/Datasets for Excel/Datasets for excel/colorbar.xlsx
+++ b/Projects/Datasets for Excel/Datasets for excel/colorbar.xlsx
@@ -1,20 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="11110"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/shahriar/Desktop/PROJECTs/Course/Data - Excel/10. color bars/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\DS\tezendra\Projects\Datasets for Excel\Datasets for excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{438C008B-DDA7-4A46-9030-17D97A0EF478}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{359099DB-D672-42AF-AA0E-E59C39B79DCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-109" yWindow="-109" windowWidth="26301" windowHeight="16520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$E$201</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -132,7 +135,54 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="5">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -432,15 +482,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:E201"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="12.1640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.625" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="12.125" style="3" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -457,7 +508,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -475,7 +526,7 @@
         <v>214.10208684011315</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -493,7 +544,7 @@
         <v>176.26324915039379</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -511,7 +562,7 @@
         <v>199.89288960977632</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -529,7 +580,7 @@
         <v>244.53743125935415</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -547,7 +598,7 @@
         <v>229.62241230254591</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -565,25 +616,25 @@
         <v>216.42790334999466</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>7</v>
+        <v>114</v>
       </c>
       <c r="B8" s="3">
-        <v>578.9606407753696</v>
+        <v>623.16210562426431</v>
       </c>
       <c r="C8" s="3">
-        <v>315.45105801625982</v>
+        <v>324.40528908001909</v>
       </c>
       <c r="D8" t="s">
         <v>7</v>
       </c>
       <c r="E8" s="3">
-        <f t="shared" si="0"/>
-        <v>263.50958275910978</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+        <f>B8-C8</f>
+        <v>298.75681654424523</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -597,11 +648,11 @@
         <v>6</v>
       </c>
       <c r="E9" s="3">
-        <f t="shared" si="0"/>
+        <f>B9-C9</f>
         <v>222.95815793027907</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
@@ -615,11 +666,11 @@
         <v>5</v>
       </c>
       <c r="E10" s="3">
-        <f t="shared" si="0"/>
+        <f>B10-C10</f>
         <v>161.07485011407095</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
@@ -633,11 +684,11 @@
         <v>5</v>
       </c>
       <c r="E11" s="3">
-        <f t="shared" si="0"/>
+        <f>B11-C11</f>
         <v>111.54605745965665</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
@@ -651,11 +702,11 @@
         <v>4</v>
       </c>
       <c r="E12" s="3">
-        <f t="shared" si="0"/>
+        <f>B12-C12</f>
         <v>159.70240003858191</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
@@ -669,11 +720,11 @@
         <v>5</v>
       </c>
       <c r="E13" s="3">
-        <f t="shared" si="0"/>
+        <f>B13-C13</f>
         <v>142.6465431160691</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
@@ -687,11 +738,11 @@
         <v>7</v>
       </c>
       <c r="E14" s="3">
-        <f t="shared" si="0"/>
+        <f>B14-C14</f>
         <v>183.47806067350564</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
@@ -705,11 +756,11 @@
         <v>4</v>
       </c>
       <c r="E15" s="3">
-        <f t="shared" si="0"/>
+        <f>B15-C15</f>
         <v>84.794250227936232</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
@@ -723,11 +774,11 @@
         <v>5</v>
       </c>
       <c r="E16" s="3">
-        <f t="shared" si="0"/>
+        <f>B16-C16</f>
         <v>123.21218571355865</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
@@ -741,11 +792,11 @@
         <v>4</v>
       </c>
       <c r="E17" s="3">
-        <f t="shared" si="0"/>
+        <f>B17-C17</f>
         <v>149.11654692315329</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
       </c>
@@ -759,11 +810,11 @@
         <v>5</v>
       </c>
       <c r="E18" s="3">
-        <f t="shared" si="0"/>
+        <f>B18-C18</f>
         <v>172.54320041940588</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
@@ -777,11 +828,11 @@
         <v>5</v>
       </c>
       <c r="E19" s="3">
-        <f t="shared" si="0"/>
+        <f>B19-C19</f>
         <v>222.81692483196395</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
@@ -795,11 +846,11 @@
         <v>5</v>
       </c>
       <c r="E20" s="3">
-        <f t="shared" si="0"/>
+        <f>B20-C20</f>
         <v>169.15970265881259</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20</v>
       </c>
@@ -813,11 +864,11 @@
         <v>7</v>
       </c>
       <c r="E21" s="3">
-        <f t="shared" si="0"/>
+        <f>B21-C21</f>
         <v>126.92859075164574</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>21</v>
       </c>
@@ -831,11 +882,11 @@
         <v>7</v>
       </c>
       <c r="E22" s="3">
-        <f t="shared" si="0"/>
+        <f>B22-C22</f>
         <v>203.84268144587247</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>22</v>
       </c>
@@ -849,11 +900,11 @@
         <v>4</v>
       </c>
       <c r="E23" s="3">
-        <f t="shared" si="0"/>
+        <f>B23-C23</f>
         <v>244.72914075342558</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>23</v>
       </c>
@@ -867,11 +918,11 @@
         <v>5</v>
       </c>
       <c r="E24" s="3">
-        <f t="shared" si="0"/>
+        <f>B24-C24</f>
         <v>182.78860452316081</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>24</v>
       </c>
@@ -885,11 +936,11 @@
         <v>5</v>
       </c>
       <c r="E25" s="3">
-        <f t="shared" si="0"/>
+        <f>B25-C25</f>
         <v>177.14406682501684</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>25</v>
       </c>
@@ -903,11 +954,11 @@
         <v>7</v>
       </c>
       <c r="E26" s="3">
-        <f t="shared" si="0"/>
+        <f>B26-C26</f>
         <v>186.93881974742391</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26</v>
       </c>
@@ -921,11 +972,11 @@
         <v>5</v>
       </c>
       <c r="E27" s="3">
-        <f t="shared" si="0"/>
+        <f>B27-C27</f>
         <v>172.8776115764723</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>27</v>
       </c>
@@ -939,11 +990,11 @@
         <v>7</v>
       </c>
       <c r="E28" s="3">
-        <f t="shared" si="0"/>
+        <f>B28-C28</f>
         <v>140.52192055602103</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>28</v>
       </c>
@@ -957,11 +1008,11 @@
         <v>5</v>
       </c>
       <c r="E29" s="3">
-        <f t="shared" si="0"/>
+        <f>B29-C29</f>
         <v>251.1172442551628</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>29</v>
       </c>
@@ -975,11 +1026,11 @@
         <v>4</v>
       </c>
       <c r="E30" s="3">
-        <f t="shared" si="0"/>
+        <f>B30-C30</f>
         <v>191.42717678185875</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>30</v>
       </c>
@@ -993,11 +1044,11 @@
         <v>5</v>
       </c>
       <c r="E31" s="3">
-        <f t="shared" si="0"/>
+        <f>B31-C31</f>
         <v>165.02738004229593</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>31</v>
       </c>
@@ -1011,29 +1062,29 @@
         <v>5</v>
       </c>
       <c r="E32" s="3">
-        <f t="shared" si="0"/>
+        <f>B32-C32</f>
         <v>191.82566834004433</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33">
-        <v>32</v>
+        <v>168</v>
       </c>
       <c r="B33" s="3">
-        <v>592.61390922544683</v>
+        <v>594.83964913269733</v>
       </c>
       <c r="C33" s="3">
-        <v>306.49375768745932</v>
+        <v>300.37777202345387</v>
       </c>
       <c r="D33" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E33" s="3">
-        <f t="shared" si="0"/>
-        <v>286.12015153798751</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
+        <f>B33-C33</f>
+        <v>294.46187710924346</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>33</v>
       </c>
@@ -1047,11 +1098,11 @@
         <v>7</v>
       </c>
       <c r="E34" s="3">
-        <f t="shared" si="0"/>
+        <f>B34-C34</f>
         <v>197.95798356598891</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>34</v>
       </c>
@@ -1065,11 +1116,11 @@
         <v>5</v>
       </c>
       <c r="E35" s="3">
-        <f t="shared" si="0"/>
+        <f>B35-C35</f>
         <v>166.66246398037953</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>35</v>
       </c>
@@ -1083,11 +1134,11 @@
         <v>5</v>
       </c>
       <c r="E36" s="3">
-        <f t="shared" si="0"/>
+        <f>B36-C36</f>
         <v>176.80892292539971</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>36</v>
       </c>
@@ -1101,11 +1152,11 @@
         <v>6</v>
       </c>
       <c r="E37" s="3">
-        <f t="shared" si="0"/>
+        <f>B37-C37</f>
         <v>119.9402468319085</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>37</v>
       </c>
@@ -1119,11 +1170,11 @@
         <v>6</v>
       </c>
       <c r="E38" s="3">
-        <f t="shared" si="0"/>
+        <f>B38-C38</f>
         <v>271.19745734996599</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>38</v>
       </c>
@@ -1137,11 +1188,11 @@
         <v>7</v>
       </c>
       <c r="E39" s="3">
-        <f t="shared" si="0"/>
+        <f>B39-C39</f>
         <v>96.422864362928408</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>39</v>
       </c>
@@ -1155,11 +1206,11 @@
         <v>6</v>
       </c>
       <c r="E40" s="3">
-        <f t="shared" si="0"/>
+        <f>B40-C40</f>
         <v>153.4442914981301</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>40</v>
       </c>
@@ -1173,11 +1224,11 @@
         <v>4</v>
       </c>
       <c r="E41" s="3">
-        <f t="shared" si="0"/>
+        <f>B41-C41</f>
         <v>184.27006174956949</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>41</v>
       </c>
@@ -1191,11 +1242,11 @@
         <v>6</v>
       </c>
       <c r="E42" s="3">
-        <f t="shared" si="0"/>
+        <f>B42-C42</f>
         <v>260.69895115275153</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>42</v>
       </c>
@@ -1209,11 +1260,11 @@
         <v>4</v>
       </c>
       <c r="E43" s="3">
-        <f t="shared" si="0"/>
+        <f>B43-C43</f>
         <v>212.01050730350551</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>43</v>
       </c>
@@ -1227,11 +1278,11 @@
         <v>7</v>
       </c>
       <c r="E44" s="3">
-        <f t="shared" si="0"/>
+        <f>B44-C44</f>
         <v>179.06796751117429</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>44</v>
       </c>
@@ -1245,11 +1296,11 @@
         <v>7</v>
       </c>
       <c r="E45" s="3">
-        <f t="shared" si="0"/>
+        <f>B45-C45</f>
         <v>158.97215939543202</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>45</v>
       </c>
@@ -1263,11 +1314,11 @@
         <v>7</v>
       </c>
       <c r="E46" s="3">
-        <f t="shared" si="0"/>
+        <f>B46-C46</f>
         <v>162.08279269330188</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>46</v>
       </c>
@@ -1281,11 +1332,11 @@
         <v>7</v>
       </c>
       <c r="E47" s="3">
-        <f t="shared" si="0"/>
+        <f>B47-C47</f>
         <v>174.042826655493</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>47</v>
       </c>
@@ -1299,11 +1350,11 @@
         <v>7</v>
       </c>
       <c r="E48" s="3">
-        <f t="shared" si="0"/>
+        <f>B48-C48</f>
         <v>191.21642078683931</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>48</v>
       </c>
@@ -1317,11 +1368,11 @@
         <v>4</v>
       </c>
       <c r="E49" s="3">
-        <f t="shared" si="0"/>
+        <f>B49-C49</f>
         <v>272.45598828815724</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>49</v>
       </c>
@@ -1335,11 +1386,11 @@
         <v>4</v>
       </c>
       <c r="E50" s="3">
-        <f t="shared" si="0"/>
+        <f>B50-C50</f>
         <v>164.21728726999021</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>50</v>
       </c>
@@ -1353,11 +1404,11 @@
         <v>7</v>
       </c>
       <c r="E51" s="3">
-        <f t="shared" si="0"/>
+        <f>B51-C51</f>
         <v>99.698540903034598</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>51</v>
       </c>
@@ -1371,11 +1422,11 @@
         <v>6</v>
       </c>
       <c r="E52" s="3">
-        <f t="shared" si="0"/>
+        <f>B52-C52</f>
         <v>254.03071709979099</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>52</v>
       </c>
@@ -1389,11 +1440,11 @@
         <v>5</v>
       </c>
       <c r="E53" s="3">
-        <f t="shared" si="0"/>
+        <f>B53-C53</f>
         <v>153.21002756754092</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>53</v>
       </c>
@@ -1407,11 +1458,11 @@
         <v>7</v>
       </c>
       <c r="E54" s="3">
-        <f t="shared" si="0"/>
+        <f>B54-C54</f>
         <v>102.48921407432312</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>54</v>
       </c>
@@ -1425,11 +1476,11 @@
         <v>6</v>
       </c>
       <c r="E55" s="3">
-        <f t="shared" si="0"/>
+        <f>B55-C55</f>
         <v>199.609856625509</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>55</v>
       </c>
@@ -1443,11 +1494,11 @@
         <v>5</v>
       </c>
       <c r="E56" s="3">
-        <f t="shared" si="0"/>
+        <f>B56-C56</f>
         <v>297.13107510341797</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>56</v>
       </c>
@@ -1461,11 +1512,11 @@
         <v>7</v>
       </c>
       <c r="E57" s="3">
-        <f t="shared" si="0"/>
+        <f>B57-C57</f>
         <v>261.09102814179749</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>57</v>
       </c>
@@ -1479,11 +1530,11 @@
         <v>7</v>
       </c>
       <c r="E58" s="3">
-        <f t="shared" si="0"/>
+        <f>B58-C58</f>
         <v>120.03178936326935</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>58</v>
       </c>
@@ -1497,11 +1548,11 @@
         <v>4</v>
       </c>
       <c r="E59" s="3">
-        <f t="shared" si="0"/>
+        <f>B59-C59</f>
         <v>205.7694651760026</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>59</v>
       </c>
@@ -1515,11 +1566,11 @@
         <v>5</v>
       </c>
       <c r="E60" s="3">
-        <f t="shared" si="0"/>
+        <f>B60-C60</f>
         <v>203.24858872579136</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>60</v>
       </c>
@@ -1533,11 +1584,11 @@
         <v>5</v>
       </c>
       <c r="E61" s="3">
-        <f t="shared" si="0"/>
+        <f>B61-C61</f>
         <v>225.53823475323787</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>61</v>
       </c>
@@ -1551,11 +1602,11 @@
         <v>6</v>
       </c>
       <c r="E62" s="3">
-        <f t="shared" si="0"/>
+        <f>B62-C62</f>
         <v>203.84920225507801</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>62</v>
       </c>
@@ -1569,11 +1620,11 @@
         <v>4</v>
       </c>
       <c r="E63" s="3">
-        <f t="shared" si="0"/>
+        <f>B63-C63</f>
         <v>192.5028118486631</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>63</v>
       </c>
@@ -1587,11 +1638,11 @@
         <v>4</v>
       </c>
       <c r="E64" s="3">
-        <f t="shared" si="0"/>
+        <f>B64-C64</f>
         <v>241.9212715017708</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>64</v>
       </c>
@@ -1605,11 +1656,11 @@
         <v>4</v>
       </c>
       <c r="E65" s="3">
-        <f t="shared" si="0"/>
+        <f>B65-C65</f>
         <v>170.92129803599511</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>65</v>
       </c>
@@ -1623,11 +1674,11 @@
         <v>4</v>
       </c>
       <c r="E66" s="3">
-        <f t="shared" si="0"/>
+        <f>B66-C66</f>
         <v>248.2033356615047</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>66</v>
       </c>
@@ -1641,11 +1692,11 @@
         <v>5</v>
       </c>
       <c r="E67" s="3">
-        <f t="shared" ref="E67:E130" si="1">B67-C67</f>
+        <f>B67-C67</f>
         <v>305.24549688748669</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>67</v>
       </c>
@@ -1659,11 +1710,11 @@
         <v>5</v>
       </c>
       <c r="E68" s="3">
-        <f t="shared" si="1"/>
+        <f>B68-C68</f>
         <v>147.42715480303428</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>68</v>
       </c>
@@ -1677,11 +1728,11 @@
         <v>7</v>
       </c>
       <c r="E69" s="3">
-        <f t="shared" si="1"/>
+        <f>B69-C69</f>
         <v>293.08088623342019</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>69</v>
       </c>
@@ -1695,11 +1746,11 @@
         <v>7</v>
       </c>
       <c r="E70" s="3">
-        <f t="shared" si="1"/>
+        <f>B70-C70</f>
         <v>231.28313585329124</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>70</v>
       </c>
@@ -1713,11 +1764,11 @@
         <v>4</v>
       </c>
       <c r="E71" s="3">
-        <f t="shared" si="1"/>
+        <f>B71-C71</f>
         <v>163.82179495116111</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>71</v>
       </c>
@@ -1731,11 +1782,11 @@
         <v>4</v>
       </c>
       <c r="E72" s="3">
-        <f t="shared" si="1"/>
+        <f>B72-C72</f>
         <v>174.8315816034372</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>72</v>
       </c>
@@ -1749,11 +1800,11 @@
         <v>4</v>
       </c>
       <c r="E73" s="3">
-        <f t="shared" si="1"/>
+        <f>B73-C73</f>
         <v>319.97769285868162</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>73</v>
       </c>
@@ -1767,29 +1818,29 @@
         <v>7</v>
       </c>
       <c r="E74" s="3">
-        <f t="shared" si="1"/>
+        <f>B74-C74</f>
         <v>163.31378547985361</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75">
-        <v>74</v>
+        <v>157</v>
       </c>
       <c r="B75" s="3">
-        <v>578.23218279070034</v>
+        <v>593.28872555723785</v>
       </c>
       <c r="C75" s="3">
-        <v>300.30699183058761</v>
+        <v>299.4446059202283</v>
       </c>
       <c r="D75" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E75" s="3">
-        <f t="shared" si="1"/>
-        <v>277.92519096011273</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.2">
+        <f>B75-C75</f>
+        <v>293.84411963700956</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>75</v>
       </c>
@@ -1803,11 +1854,11 @@
         <v>6</v>
       </c>
       <c r="E76" s="3">
-        <f t="shared" si="1"/>
+        <f>B76-C76</f>
         <v>98.458004326951311</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>76</v>
       </c>
@@ -1821,11 +1872,11 @@
         <v>7</v>
       </c>
       <c r="E77" s="3">
-        <f t="shared" si="1"/>
+        <f>B77-C77</f>
         <v>227.23202099086308</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>77</v>
       </c>
@@ -1839,11 +1890,11 @@
         <v>7</v>
       </c>
       <c r="E78" s="3">
-        <f t="shared" si="1"/>
+        <f>B78-C78</f>
         <v>198.3805625447045</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>78</v>
       </c>
@@ -1857,11 +1908,11 @@
         <v>7</v>
       </c>
       <c r="E79" s="3">
-        <f t="shared" si="1"/>
+        <f>B79-C79</f>
         <v>203.0561387914704</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>79</v>
       </c>
@@ -1875,11 +1926,11 @@
         <v>7</v>
       </c>
       <c r="E80" s="3">
-        <f t="shared" si="1"/>
+        <f>B80-C80</f>
         <v>202.49397627707452</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>80</v>
       </c>
@@ -1893,11 +1944,11 @@
         <v>7</v>
       </c>
       <c r="E81" s="3">
-        <f t="shared" si="1"/>
+        <f>B81-C81</f>
         <v>112.18096217580825</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>81</v>
       </c>
@@ -1911,11 +1962,11 @@
         <v>7</v>
       </c>
       <c r="E82" s="3">
-        <f t="shared" si="1"/>
+        <f>B82-C82</f>
         <v>185.61088525058688</v>
       </c>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>82</v>
       </c>
@@ -1929,11 +1980,11 @@
         <v>4</v>
       </c>
       <c r="E83" s="3">
-        <f t="shared" si="1"/>
+        <f>B83-C83</f>
         <v>197.99170833995589</v>
       </c>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>83</v>
       </c>
@@ -1947,11 +1998,11 @@
         <v>4</v>
       </c>
       <c r="E84" s="3">
-        <f t="shared" si="1"/>
+        <f>B84-C84</f>
         <v>226.31419775271519</v>
       </c>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>84</v>
       </c>
@@ -1965,11 +2016,11 @@
         <v>4</v>
       </c>
       <c r="E85" s="3">
-        <f t="shared" si="1"/>
+        <f>B85-C85</f>
         <v>211.2209540511231</v>
       </c>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>85</v>
       </c>
@@ -1983,11 +2034,11 @@
         <v>4</v>
       </c>
       <c r="E86" s="3">
-        <f t="shared" si="1"/>
+        <f>B86-C86</f>
         <v>95.584318615652592</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>86</v>
       </c>
@@ -2001,11 +2052,11 @@
         <v>7</v>
       </c>
       <c r="E87" s="3">
-        <f t="shared" si="1"/>
+        <f>B87-C87</f>
         <v>233.47478180644831</v>
       </c>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>87</v>
       </c>
@@ -2019,11 +2070,11 @@
         <v>6</v>
       </c>
       <c r="E88" s="3">
-        <f t="shared" si="1"/>
+        <f>B88-C88</f>
         <v>250.32365873617118</v>
       </c>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>88</v>
       </c>
@@ -2037,11 +2088,11 @@
         <v>5</v>
       </c>
       <c r="E89" s="3">
-        <f t="shared" si="1"/>
+        <f>B89-C89</f>
         <v>198.7880392884469</v>
       </c>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>89</v>
       </c>
@@ -2055,11 +2106,11 @@
         <v>7</v>
       </c>
       <c r="E90" s="3">
-        <f t="shared" si="1"/>
+        <f>B90-C90</f>
         <v>165.082233779597</v>
       </c>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>90</v>
       </c>
@@ -2073,11 +2124,11 @@
         <v>5</v>
       </c>
       <c r="E91" s="3">
-        <f t="shared" si="1"/>
+        <f>B91-C91</f>
         <v>244.34435725028561</v>
       </c>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>91</v>
       </c>
@@ -2091,11 +2142,11 @@
         <v>6</v>
       </c>
       <c r="E92" s="3">
-        <f t="shared" si="1"/>
+        <f>B92-C92</f>
         <v>211.0975449781202</v>
       </c>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>92</v>
       </c>
@@ -2109,11 +2160,11 @@
         <v>4</v>
       </c>
       <c r="E93" s="3">
-        <f t="shared" si="1"/>
+        <f>B93-C93</f>
         <v>263.22227756640945</v>
       </c>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>93</v>
       </c>
@@ -2127,11 +2178,11 @@
         <v>6</v>
       </c>
       <c r="E94" s="3">
-        <f t="shared" si="1"/>
+        <f>B94-C94</f>
         <v>182.57828801445885</v>
       </c>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>94</v>
       </c>
@@ -2145,11 +2196,11 @@
         <v>7</v>
       </c>
       <c r="E95" s="3">
-        <f t="shared" si="1"/>
+        <f>B95-C95</f>
         <v>158.12882975948094</v>
       </c>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>95</v>
       </c>
@@ -2163,11 +2214,11 @@
         <v>4</v>
       </c>
       <c r="E96" s="3">
-        <f t="shared" si="1"/>
+        <f>B96-C96</f>
         <v>169.68412776444069</v>
       </c>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>96</v>
       </c>
@@ -2181,11 +2232,11 @@
         <v>7</v>
       </c>
       <c r="E97" s="3">
-        <f t="shared" si="1"/>
+        <f>B97-C97</f>
         <v>147.61154045121367</v>
       </c>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>97</v>
       </c>
@@ -2199,11 +2250,11 @@
         <v>4</v>
       </c>
       <c r="E98" s="3">
-        <f t="shared" si="1"/>
+        <f>B98-C98</f>
         <v>187.81801759023131</v>
       </c>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>98</v>
       </c>
@@ -2217,11 +2268,11 @@
         <v>5</v>
       </c>
       <c r="E99" s="3">
-        <f t="shared" si="1"/>
+        <f>B99-C99</f>
         <v>203.83377798269618</v>
       </c>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>99</v>
       </c>
@@ -2235,11 +2286,11 @@
         <v>5</v>
       </c>
       <c r="E100" s="3">
-        <f t="shared" si="1"/>
+        <f>B100-C100</f>
         <v>175.86980926695423</v>
       </c>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>100</v>
       </c>
@@ -2253,11 +2304,11 @@
         <v>5</v>
       </c>
       <c r="E101" s="3">
-        <f t="shared" si="1"/>
+        <f>B101-C101</f>
         <v>169.38177807353429</v>
       </c>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A102">
         <v>101</v>
       </c>
@@ -2271,11 +2322,11 @@
         <v>6</v>
       </c>
       <c r="E102" s="3">
-        <f t="shared" si="1"/>
+        <f>B102-C102</f>
         <v>154.1013132251415</v>
       </c>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103">
         <v>102</v>
       </c>
@@ -2289,11 +2340,11 @@
         <v>7</v>
       </c>
       <c r="E103" s="3">
-        <f t="shared" si="1"/>
+        <f>B103-C103</f>
         <v>195.77316506764106</v>
       </c>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A104">
         <v>103</v>
       </c>
@@ -2307,11 +2358,11 @@
         <v>6</v>
       </c>
       <c r="E104" s="3">
-        <f t="shared" si="1"/>
+        <f>B104-C104</f>
         <v>160.44546601996359</v>
       </c>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A105">
         <v>104</v>
       </c>
@@ -2325,11 +2376,11 @@
         <v>5</v>
       </c>
       <c r="E105" s="3">
-        <f t="shared" si="1"/>
+        <f>B105-C105</f>
         <v>141.5750285759151</v>
       </c>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A106">
         <v>105</v>
       </c>
@@ -2343,11 +2394,11 @@
         <v>7</v>
       </c>
       <c r="E106" s="3">
-        <f t="shared" si="1"/>
+        <f>B106-C106</f>
         <v>192.56276223562401</v>
       </c>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A107">
         <v>106</v>
       </c>
@@ -2361,29 +2412,29 @@
         <v>5</v>
       </c>
       <c r="E107" s="3">
-        <f t="shared" si="1"/>
+        <f>B107-C107</f>
         <v>216.68272134146338</v>
       </c>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A108">
-        <v>107</v>
+        <v>32</v>
       </c>
       <c r="B108" s="3">
-        <v>594.30929506052655</v>
+        <v>592.61390922544683</v>
       </c>
       <c r="C108" s="3">
-        <v>338.32994687365272</v>
+        <v>306.49375768745932</v>
       </c>
       <c r="D108" t="s">
         <v>6</v>
       </c>
       <c r="E108" s="3">
-        <f t="shared" si="1"/>
-        <v>255.97934818687384</v>
-      </c>
-    </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.2">
+        <f>B108-C108</f>
+        <v>286.12015153798751</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A109">
         <v>108</v>
       </c>
@@ -2397,11 +2448,11 @@
         <v>6</v>
       </c>
       <c r="E109" s="3">
-        <f t="shared" si="1"/>
+        <f>B109-C109</f>
         <v>226.47603230666675</v>
       </c>
     </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A110">
         <v>109</v>
       </c>
@@ -2415,11 +2466,11 @@
         <v>6</v>
       </c>
       <c r="E110" s="3">
-        <f t="shared" si="1"/>
+        <f>B110-C110</f>
         <v>196.46459810103715</v>
       </c>
     </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A111">
         <v>110</v>
       </c>
@@ -2433,11 +2484,11 @@
         <v>5</v>
       </c>
       <c r="E111" s="3">
-        <f t="shared" si="1"/>
+        <f>B111-C111</f>
         <v>202.34348378470844</v>
       </c>
     </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A112">
         <v>111</v>
       </c>
@@ -2451,11 +2502,11 @@
         <v>7</v>
       </c>
       <c r="E112" s="3">
-        <f t="shared" si="1"/>
+        <f>B112-C112</f>
         <v>110.59187533186446</v>
       </c>
     </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A113">
         <v>112</v>
       </c>
@@ -2469,11 +2520,11 @@
         <v>7</v>
       </c>
       <c r="E113" s="3">
-        <f t="shared" si="1"/>
+        <f>B113-C113</f>
         <v>165.71100066792337</v>
       </c>
     </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A114">
         <v>113</v>
       </c>
@@ -2487,29 +2538,29 @@
         <v>5</v>
       </c>
       <c r="E114" s="3">
-        <f t="shared" si="1"/>
+        <f>B114-C114</f>
         <v>178.24902002741038</v>
       </c>
     </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A115">
-        <v>114</v>
+        <v>136</v>
       </c>
       <c r="B115" s="3">
-        <v>623.16210562426431</v>
+        <v>577.49672025087693</v>
       </c>
       <c r="C115" s="3">
-        <v>324.40528908001909</v>
+        <v>295.58827855493593</v>
       </c>
       <c r="D115" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E115" s="3">
-        <f t="shared" si="1"/>
-        <v>298.75681654424523</v>
-      </c>
-    </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.2">
+        <f>B115-C115</f>
+        <v>281.90844169594101</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A116">
         <v>115</v>
       </c>
@@ -2523,11 +2574,11 @@
         <v>5</v>
       </c>
       <c r="E116" s="3">
-        <f t="shared" si="1"/>
+        <f>B116-C116</f>
         <v>151.21758754631395</v>
       </c>
     </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A117">
         <v>116</v>
       </c>
@@ -2541,11 +2592,11 @@
         <v>7</v>
       </c>
       <c r="E117" s="3">
-        <f t="shared" si="1"/>
+        <f>B117-C117</f>
         <v>214.44725186769796</v>
       </c>
     </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A118">
         <v>117</v>
       </c>
@@ -2559,11 +2610,11 @@
         <v>4</v>
       </c>
       <c r="E118" s="3">
-        <f t="shared" si="1"/>
+        <f>B118-C118</f>
         <v>177.80582237588891</v>
       </c>
     </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A119">
         <v>118</v>
       </c>
@@ -2577,11 +2628,11 @@
         <v>4</v>
       </c>
       <c r="E119" s="3">
-        <f t="shared" si="1"/>
+        <f>B119-C119</f>
         <v>150.87410081682714</v>
       </c>
     </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A120">
         <v>119</v>
       </c>
@@ -2595,11 +2646,11 @@
         <v>6</v>
       </c>
       <c r="E120" s="3">
-        <f t="shared" si="1"/>
+        <f>B120-C120</f>
         <v>247.41615015109784</v>
       </c>
     </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A121">
         <v>120</v>
       </c>
@@ -2613,11 +2664,11 @@
         <v>4</v>
       </c>
       <c r="E121" s="3">
-        <f t="shared" si="1"/>
+        <f>B121-C121</f>
         <v>241.50094326536936</v>
       </c>
     </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A122">
         <v>121</v>
       </c>
@@ -2631,11 +2682,11 @@
         <v>4</v>
       </c>
       <c r="E122" s="3">
-        <f t="shared" si="1"/>
+        <f>B122-C122</f>
         <v>236.64171840237077</v>
       </c>
     </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A123">
         <v>122</v>
       </c>
@@ -2649,11 +2700,11 @@
         <v>4</v>
       </c>
       <c r="E123" s="3">
-        <f t="shared" si="1"/>
+        <f>B123-C123</f>
         <v>136.67591649715558</v>
       </c>
     </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A124">
         <v>123</v>
       </c>
@@ -2667,11 +2718,11 @@
         <v>5</v>
       </c>
       <c r="E124" s="3">
-        <f t="shared" si="1"/>
+        <f>B124-C124</f>
         <v>294.68633604380915</v>
       </c>
     </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A125">
         <v>124</v>
       </c>
@@ -2685,11 +2736,11 @@
         <v>4</v>
       </c>
       <c r="E125" s="3">
-        <f t="shared" si="1"/>
+        <f>B125-C125</f>
         <v>67.135828589822211</v>
       </c>
     </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A126">
         <v>125</v>
       </c>
@@ -2703,11 +2754,11 @@
         <v>4</v>
       </c>
       <c r="E126" s="3">
-        <f t="shared" si="1"/>
+        <f>B126-C126</f>
         <v>259.52337613500458</v>
       </c>
     </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A127">
         <v>126</v>
       </c>
@@ -2721,11 +2772,11 @@
         <v>6</v>
       </c>
       <c r="E127" s="3">
-        <f t="shared" si="1"/>
+        <f>B127-C127</f>
         <v>345.9484396741309</v>
       </c>
     </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A128">
         <v>127</v>
       </c>
@@ -2739,11 +2790,11 @@
         <v>4</v>
       </c>
       <c r="E128" s="3">
-        <f t="shared" si="1"/>
+        <f>B128-C128</f>
         <v>115.72985753846348</v>
       </c>
     </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A129">
         <v>128</v>
       </c>
@@ -2757,11 +2808,11 @@
         <v>4</v>
       </c>
       <c r="E129" s="3">
-        <f t="shared" si="1"/>
+        <f>B129-C129</f>
         <v>147.9352327009733</v>
       </c>
     </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A130">
         <v>129</v>
       </c>
@@ -2775,11 +2826,11 @@
         <v>7</v>
       </c>
       <c r="E130" s="3">
-        <f t="shared" si="1"/>
+        <f>B130-C130</f>
         <v>186.25897374281726</v>
       </c>
     </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A131">
         <v>130</v>
       </c>
@@ -2793,11 +2844,11 @@
         <v>6</v>
       </c>
       <c r="E131" s="3">
-        <f t="shared" ref="E131:E194" si="2">B131-C131</f>
+        <f>B131-C131</f>
         <v>155.97585201626157</v>
       </c>
     </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A132">
         <v>131</v>
       </c>
@@ -2811,11 +2862,11 @@
         <v>6</v>
       </c>
       <c r="E132" s="3">
-        <f t="shared" si="2"/>
+        <f>B132-C132</f>
         <v>122.83423163210091</v>
       </c>
     </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A133">
         <v>132</v>
       </c>
@@ -2829,11 +2880,11 @@
         <v>6</v>
       </c>
       <c r="E133" s="3">
-        <f t="shared" si="2"/>
+        <f>B133-C133</f>
         <v>230.34577988487644</v>
       </c>
     </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A134">
         <v>133</v>
       </c>
@@ -2847,11 +2898,11 @@
         <v>6</v>
       </c>
       <c r="E134" s="3">
-        <f t="shared" si="2"/>
+        <f>B134-C134</f>
         <v>144.61067756788287</v>
       </c>
     </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A135">
         <v>134</v>
       </c>
@@ -2865,11 +2916,11 @@
         <v>6</v>
       </c>
       <c r="E135" s="3">
-        <f t="shared" si="2"/>
+        <f>B135-C135</f>
         <v>243.99447287712246</v>
       </c>
     </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A136">
         <v>135</v>
       </c>
@@ -2883,29 +2934,29 @@
         <v>6</v>
       </c>
       <c r="E136" s="3">
-        <f t="shared" si="2"/>
+        <f>B136-C136</f>
         <v>124.77519628577727</v>
       </c>
     </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A137">
-        <v>136</v>
+        <v>74</v>
       </c>
       <c r="B137" s="3">
-        <v>577.49672025087693</v>
+        <v>578.23218279070034</v>
       </c>
       <c r="C137" s="3">
-        <v>295.58827855493593</v>
+        <v>300.30699183058761</v>
       </c>
       <c r="D137" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E137" s="3">
-        <f t="shared" si="2"/>
-        <v>281.90844169594101</v>
-      </c>
-    </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.2">
+        <f>B137-C137</f>
+        <v>277.92519096011273</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A138">
         <v>137</v>
       </c>
@@ -2919,11 +2970,11 @@
         <v>4</v>
       </c>
       <c r="E138" s="3">
-        <f t="shared" si="2"/>
+        <f>B138-C138</f>
         <v>185.60225128696339</v>
       </c>
     </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A139">
         <v>138</v>
       </c>
@@ -2937,11 +2988,11 @@
         <v>6</v>
       </c>
       <c r="E139" s="3">
-        <f t="shared" si="2"/>
+        <f>B139-C139</f>
         <v>193.53849943930595</v>
       </c>
     </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A140">
         <v>139</v>
       </c>
@@ -2955,11 +3006,11 @@
         <v>4</v>
       </c>
       <c r="E140" s="3">
-        <f t="shared" si="2"/>
+        <f>B140-C140</f>
         <v>228.28791724021477</v>
       </c>
     </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A141">
         <v>140</v>
       </c>
@@ -2973,11 +3024,11 @@
         <v>4</v>
       </c>
       <c r="E141" s="3">
-        <f t="shared" si="2"/>
+        <f>B141-C141</f>
         <v>155.3685207624215</v>
       </c>
     </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A142">
         <v>141</v>
       </c>
@@ -2991,11 +3042,11 @@
         <v>5</v>
       </c>
       <c r="E142" s="3">
-        <f t="shared" si="2"/>
+        <f>B142-C142</f>
         <v>236.03960859719945</v>
       </c>
     </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A143">
         <v>142</v>
       </c>
@@ -3009,11 +3060,11 @@
         <v>6</v>
       </c>
       <c r="E143" s="3">
-        <f t="shared" si="2"/>
+        <f>B143-C143</f>
         <v>258.04652136936403</v>
       </c>
     </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A144">
         <v>143</v>
       </c>
@@ -3027,11 +3078,11 @@
         <v>7</v>
       </c>
       <c r="E144" s="3">
-        <f t="shared" si="2"/>
+        <f>B144-C144</f>
         <v>112.2768411386769</v>
       </c>
     </row>
-    <row r="145" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A145">
         <v>144</v>
       </c>
@@ -3045,11 +3096,11 @@
         <v>5</v>
       </c>
       <c r="E145" s="3">
-        <f t="shared" si="2"/>
+        <f>B145-C145</f>
         <v>224.43998818774912</v>
       </c>
     </row>
-    <row r="146" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A146">
         <v>145</v>
       </c>
@@ -3063,11 +3114,11 @@
         <v>7</v>
       </c>
       <c r="E146" s="3">
-        <f t="shared" si="2"/>
+        <f>B146-C146</f>
         <v>227.12528888097091</v>
       </c>
     </row>
-    <row r="147" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A147">
         <v>146</v>
       </c>
@@ -3081,11 +3132,11 @@
         <v>4</v>
       </c>
       <c r="E147" s="3">
-        <f t="shared" si="2"/>
+        <f>B147-C147</f>
         <v>232.1296454681364</v>
       </c>
     </row>
-    <row r="148" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A148">
         <v>147</v>
       </c>
@@ -3099,11 +3150,11 @@
         <v>4</v>
       </c>
       <c r="E148" s="3">
-        <f t="shared" si="2"/>
+        <f>B148-C148</f>
         <v>181.59499470101559</v>
       </c>
     </row>
-    <row r="149" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A149">
         <v>148</v>
       </c>
@@ -3117,11 +3168,11 @@
         <v>5</v>
       </c>
       <c r="E149" s="3">
-        <f t="shared" si="2"/>
+        <f>B149-C149</f>
         <v>176.20108257708279</v>
       </c>
     </row>
-    <row r="150" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A150">
         <v>149</v>
       </c>
@@ -3135,11 +3186,11 @@
         <v>5</v>
       </c>
       <c r="E150" s="3">
-        <f t="shared" si="2"/>
+        <f>B150-C150</f>
         <v>247.65040491841802</v>
       </c>
     </row>
-    <row r="151" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A151">
         <v>150</v>
       </c>
@@ -3153,11 +3204,11 @@
         <v>7</v>
       </c>
       <c r="E151" s="3">
-        <f t="shared" si="2"/>
+        <f>B151-C151</f>
         <v>221.25264821301477</v>
       </c>
     </row>
-    <row r="152" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A152">
         <v>151</v>
       </c>
@@ -3171,11 +3222,11 @@
         <v>6</v>
       </c>
       <c r="E152" s="3">
-        <f t="shared" si="2"/>
+        <f>B152-C152</f>
         <v>203.19741554935376</v>
       </c>
     </row>
-    <row r="153" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A153">
         <v>152</v>
       </c>
@@ -3189,11 +3240,11 @@
         <v>7</v>
       </c>
       <c r="E153" s="3">
-        <f t="shared" si="2"/>
+        <f>B153-C153</f>
         <v>173.06172396636219</v>
       </c>
     </row>
-    <row r="154" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A154">
         <v>153</v>
       </c>
@@ -3207,11 +3258,11 @@
         <v>5</v>
       </c>
       <c r="E154" s="3">
-        <f t="shared" si="2"/>
+        <f>B154-C154</f>
         <v>140.26897522501491</v>
       </c>
     </row>
-    <row r="155" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A155">
         <v>154</v>
       </c>
@@ -3225,11 +3276,11 @@
         <v>7</v>
       </c>
       <c r="E155" s="3">
-        <f t="shared" si="2"/>
+        <f>B155-C155</f>
         <v>216.41084075695301</v>
       </c>
     </row>
-    <row r="156" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A156">
         <v>155</v>
       </c>
@@ -3243,11 +3294,11 @@
         <v>5</v>
       </c>
       <c r="E156" s="3">
-        <f t="shared" si="2"/>
+        <f>B156-C156</f>
         <v>215.22410990201479</v>
       </c>
     </row>
-    <row r="157" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A157">
         <v>156</v>
       </c>
@@ -3261,29 +3312,29 @@
         <v>7</v>
       </c>
       <c r="E157" s="3">
-        <f t="shared" si="2"/>
+        <f>B157-C157</f>
         <v>194.3583100378159</v>
       </c>
     </row>
-    <row r="158" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A158">
-        <v>157</v>
+        <v>7</v>
       </c>
       <c r="B158" s="3">
-        <v>593.28872555723785</v>
+        <v>578.9606407753696</v>
       </c>
       <c r="C158" s="3">
-        <v>299.4446059202283</v>
+        <v>315.45105801625982</v>
       </c>
       <c r="D158" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E158" s="3">
-        <f t="shared" si="2"/>
-        <v>293.84411963700956</v>
-      </c>
-    </row>
-    <row r="159" spans="1:5" x14ac:dyDescent="0.2">
+        <f>B158-C158</f>
+        <v>263.50958275910978</v>
+      </c>
+    </row>
+    <row r="159" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A159">
         <v>158</v>
       </c>
@@ -3297,11 +3348,11 @@
         <v>5</v>
       </c>
       <c r="E159" s="3">
-        <f t="shared" si="2"/>
+        <f>B159-C159</f>
         <v>232.3514052131934</v>
       </c>
     </row>
-    <row r="160" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A160">
         <v>159</v>
       </c>
@@ -3315,11 +3366,11 @@
         <v>5</v>
       </c>
       <c r="E160" s="3">
-        <f t="shared" si="2"/>
+        <f>B160-C160</f>
         <v>130.7532683297249</v>
       </c>
     </row>
-    <row r="161" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A161">
         <v>160</v>
       </c>
@@ -3333,11 +3384,11 @@
         <v>6</v>
       </c>
       <c r="E161" s="3">
-        <f t="shared" si="2"/>
+        <f>B161-C161</f>
         <v>257.64460873826124</v>
       </c>
     </row>
-    <row r="162" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A162">
         <v>161</v>
       </c>
@@ -3351,11 +3402,11 @@
         <v>7</v>
       </c>
       <c r="E162" s="3">
-        <f t="shared" si="2"/>
+        <f>B162-C162</f>
         <v>135.68552106139879</v>
       </c>
     </row>
-    <row r="163" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A163">
         <v>162</v>
       </c>
@@ -3369,11 +3420,11 @@
         <v>7</v>
       </c>
       <c r="E163" s="3">
-        <f t="shared" si="2"/>
+        <f>B163-C163</f>
         <v>193.37206279704537</v>
       </c>
     </row>
-    <row r="164" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A164">
         <v>163</v>
       </c>
@@ -3387,11 +3438,11 @@
         <v>7</v>
       </c>
       <c r="E164" s="3">
-        <f t="shared" si="2"/>
+        <f>B164-C164</f>
         <v>261.19258340407589</v>
       </c>
     </row>
-    <row r="165" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A165">
         <v>164</v>
       </c>
@@ -3405,11 +3456,11 @@
         <v>5</v>
       </c>
       <c r="E165" s="3">
-        <f t="shared" si="2"/>
+        <f>B165-C165</f>
         <v>146.91453241944623</v>
       </c>
     </row>
-    <row r="166" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A166">
         <v>165</v>
       </c>
@@ -3423,11 +3474,11 @@
         <v>7</v>
       </c>
       <c r="E166" s="3">
-        <f t="shared" si="2"/>
+        <f>B166-C166</f>
         <v>227.46448671088274</v>
       </c>
     </row>
-    <row r="167" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A167">
         <v>166</v>
       </c>
@@ -3441,11 +3492,11 @@
         <v>7</v>
       </c>
       <c r="E167" s="3">
-        <f t="shared" si="2"/>
+        <f>B167-C167</f>
         <v>232.67566050340002</v>
       </c>
     </row>
-    <row r="168" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A168">
         <v>167</v>
       </c>
@@ -3459,29 +3510,29 @@
         <v>5</v>
       </c>
       <c r="E168" s="3">
-        <f t="shared" si="2"/>
+        <f>B168-C168</f>
         <v>234.38023354541195</v>
       </c>
     </row>
-    <row r="169" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A169">
-        <v>168</v>
+        <v>107</v>
       </c>
       <c r="B169" s="3">
-        <v>594.83964913269733</v>
+        <v>594.30929506052655</v>
       </c>
       <c r="C169" s="3">
-        <v>300.37777202345387</v>
+        <v>338.32994687365272</v>
       </c>
       <c r="D169" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E169" s="3">
-        <f t="shared" si="2"/>
-        <v>294.46187710924346</v>
-      </c>
-    </row>
-    <row r="170" spans="1:5" x14ac:dyDescent="0.2">
+        <f>B169-C169</f>
+        <v>255.97934818687384</v>
+      </c>
+    </row>
+    <row r="170" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A170">
         <v>169</v>
       </c>
@@ -3495,11 +3546,11 @@
         <v>5</v>
       </c>
       <c r="E170" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="E131:E194" si="1">B170-C170</f>
         <v>184.80031124339149</v>
       </c>
     </row>
-    <row r="171" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A171">
         <v>170</v>
       </c>
@@ -3513,11 +3564,11 @@
         <v>7</v>
       </c>
       <c r="E171" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>185.5034852977895</v>
       </c>
     </row>
-    <row r="172" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A172">
         <v>171</v>
       </c>
@@ -3531,11 +3582,11 @@
         <v>5</v>
       </c>
       <c r="E172" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>154.78897329095548</v>
       </c>
     </row>
-    <row r="173" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A173">
         <v>172</v>
       </c>
@@ -3549,11 +3600,11 @@
         <v>4</v>
       </c>
       <c r="E173" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>144.26953701436457</v>
       </c>
     </row>
-    <row r="174" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A174">
         <v>173</v>
       </c>
@@ -3567,11 +3618,11 @@
         <v>5</v>
       </c>
       <c r="E174" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>152.61060629544357</v>
       </c>
     </row>
-    <row r="175" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A175">
         <v>174</v>
       </c>
@@ -3585,11 +3636,11 @@
         <v>7</v>
       </c>
       <c r="E175" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>188.27947395827601</v>
       </c>
     </row>
-    <row r="176" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A176">
         <v>175</v>
       </c>
@@ -3603,11 +3654,11 @@
         <v>4</v>
       </c>
       <c r="E176" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>149.23906624115426</v>
       </c>
     </row>
-    <row r="177" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A177">
         <v>176</v>
       </c>
@@ -3621,11 +3672,11 @@
         <v>6</v>
       </c>
       <c r="E177" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>264.37958933844271</v>
       </c>
     </row>
-    <row r="178" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A178">
         <v>177</v>
       </c>
@@ -3639,11 +3690,11 @@
         <v>7</v>
       </c>
       <c r="E178" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>174.48047549227488</v>
       </c>
     </row>
-    <row r="179" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A179">
         <v>178</v>
       </c>
@@ -3657,11 +3708,11 @@
         <v>4</v>
       </c>
       <c r="E179" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>267.17644368571536</v>
       </c>
     </row>
-    <row r="180" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A180">
         <v>179</v>
       </c>
@@ -3675,11 +3726,11 @@
         <v>4</v>
       </c>
       <c r="E180" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>121.07307034157202</v>
       </c>
     </row>
-    <row r="181" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A181">
         <v>180</v>
       </c>
@@ -3693,11 +3744,11 @@
         <v>6</v>
       </c>
       <c r="E181" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>360.25740689013548</v>
       </c>
     </row>
-    <row r="182" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A182">
         <v>181</v>
       </c>
@@ -3711,11 +3762,11 @@
         <v>5</v>
       </c>
       <c r="E182" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>256.47502265367365</v>
       </c>
     </row>
-    <row r="183" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A183">
         <v>182</v>
       </c>
@@ -3729,11 +3780,11 @@
         <v>5</v>
       </c>
       <c r="E183" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>175.12390154250647</v>
       </c>
     </row>
-    <row r="184" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A184">
         <v>183</v>
       </c>
@@ -3747,11 +3798,11 @@
         <v>7</v>
       </c>
       <c r="E184" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>210.17224682623862</v>
       </c>
     </row>
-    <row r="185" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A185">
         <v>184</v>
       </c>
@@ -3765,11 +3816,11 @@
         <v>6</v>
       </c>
       <c r="E185" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>239.89627141258205</v>
       </c>
     </row>
-    <row r="186" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A186">
         <v>185</v>
       </c>
@@ -3783,11 +3834,11 @@
         <v>5</v>
       </c>
       <c r="E186" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>211.60084058031845</v>
       </c>
     </row>
-    <row r="187" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A187">
         <v>186</v>
       </c>
@@ -3801,11 +3852,11 @@
         <v>6</v>
       </c>
       <c r="E187" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>231.18821111031832</v>
       </c>
     </row>
-    <row r="188" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A188">
         <v>187</v>
       </c>
@@ -3819,11 +3870,11 @@
         <v>5</v>
       </c>
       <c r="E188" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>213.40920195536239</v>
       </c>
     </row>
-    <row r="189" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A189">
         <v>188</v>
       </c>
@@ -3837,11 +3888,11 @@
         <v>4</v>
       </c>
       <c r="E189" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>140.0734291906798</v>
       </c>
     </row>
-    <row r="190" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A190">
         <v>189</v>
       </c>
@@ -3855,11 +3906,11 @@
         <v>5</v>
       </c>
       <c r="E190" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>129.14759895099826</v>
       </c>
     </row>
-    <row r="191" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A191">
         <v>190</v>
       </c>
@@ -3873,11 +3924,11 @@
         <v>6</v>
       </c>
       <c r="E191" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>141.56474843557891</v>
       </c>
     </row>
-    <row r="192" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A192">
         <v>191</v>
       </c>
@@ -3891,11 +3942,11 @@
         <v>4</v>
       </c>
       <c r="E192" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>204.6266925370997</v>
       </c>
     </row>
-    <row r="193" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A193">
         <v>192</v>
       </c>
@@ -3909,11 +3960,11 @@
         <v>4</v>
       </c>
       <c r="E193" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>228.06236457097845</v>
       </c>
     </row>
-    <row r="194" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A194">
         <v>193</v>
       </c>
@@ -3927,11 +3978,11 @@
         <v>4</v>
       </c>
       <c r="E194" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>250.31168341712947</v>
       </c>
     </row>
-    <row r="195" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A195">
         <v>194</v>
       </c>
@@ -3945,11 +3996,11 @@
         <v>6</v>
       </c>
       <c r="E195" s="3">
-        <f t="shared" ref="E195:E201" si="3">B195-C195</f>
+        <f t="shared" ref="E195:E201" si="2">B195-C195</f>
         <v>82.769298088770029</v>
       </c>
     </row>
-    <row r="196" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A196">
         <v>195</v>
       </c>
@@ -3963,11 +4014,11 @@
         <v>7</v>
       </c>
       <c r="E196" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>173.2758426709205</v>
       </c>
     </row>
-    <row r="197" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A197">
         <v>196</v>
       </c>
@@ -3981,11 +4032,11 @@
         <v>7</v>
       </c>
       <c r="E197" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>233.34113854958298</v>
       </c>
     </row>
-    <row r="198" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A198">
         <v>197</v>
       </c>
@@ -3999,11 +4050,11 @@
         <v>7</v>
       </c>
       <c r="E198" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>207.20116406266959</v>
       </c>
     </row>
-    <row r="199" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A199">
         <v>198</v>
       </c>
@@ -4017,11 +4068,11 @@
         <v>6</v>
       </c>
       <c r="E199" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>167.07008407231399</v>
       </c>
     </row>
-    <row r="200" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A200">
         <v>199</v>
       </c>
@@ -4035,11 +4086,11 @@
         <v>4</v>
       </c>
       <c r="E200" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>206.34663127987852</v>
       </c>
     </row>
-    <row r="201" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A201">
         <v>200</v>
       </c>
@@ -4053,11 +4104,30 @@
         <v>7</v>
       </c>
       <c r="E201" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>105.7169957492651</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:E201" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="1">
+      <colorFilter dxfId="4"/>
+    </filterColumn>
+    <filterColumn colId="4">
+      <colorFilter dxfId="0"/>
+    </filterColumn>
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A8:E169">
+      <sortCondition descending="1" ref="E1:E201"/>
+    </sortState>
+  </autoFilter>
+  <conditionalFormatting sqref="B1:B1048576">
+    <cfRule type="top10" dxfId="3" priority="2" rank="10"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E1:E1048576">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
+      <formula>300</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>